--- a/artfynd/A 46787-2024 artfynd.xlsx
+++ b/artfynd/A 46787-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121432350</v>
+        <v>121432657</v>
       </c>
       <c r="B3" t="n">
-        <v>79682</v>
+        <v>90697</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520544</v>
+        <v>520484</v>
       </c>
       <c r="R3" t="n">
-        <v>6995746</v>
+        <v>6995781</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121432657</v>
+        <v>121432350</v>
       </c>
       <c r="B4" t="n">
-        <v>90697</v>
+        <v>79682</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520484</v>
+        <v>520544</v>
       </c>
       <c r="R4" t="n">
-        <v>6995781</v>
+        <v>6995746</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 46787-2024 artfynd.xlsx
+++ b/artfynd/A 46787-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121432782</v>
       </c>
       <c r="B2" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121432657</v>
+        <v>121432350</v>
       </c>
       <c r="B3" t="n">
-        <v>90697</v>
+        <v>79685</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520484</v>
+        <v>520544</v>
       </c>
       <c r="R3" t="n">
-        <v>6995781</v>
+        <v>6995746</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121432350</v>
+        <v>121432657</v>
       </c>
       <c r="B4" t="n">
-        <v>79682</v>
+        <v>90709</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520544</v>
+        <v>520484</v>
       </c>
       <c r="R4" t="n">
-        <v>6995746</v>
+        <v>6995781</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 46787-2024 artfynd.xlsx
+++ b/artfynd/A 46787-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121432782</v>
+        <v>121432350</v>
       </c>
       <c r="B2" t="n">
         <v>79685</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520435</v>
+        <v>520544</v>
       </c>
       <c r="R2" t="n">
-        <v>6995794</v>
+        <v>6995746</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121432350</v>
+        <v>121432782</v>
       </c>
       <c r="B3" t="n">
         <v>79685</v>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520544</v>
+        <v>520435</v>
       </c>
       <c r="R3" t="n">
-        <v>6995746</v>
+        <v>6995794</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
         <v>121432657</v>
       </c>
       <c r="B4" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 46787-2024 artfynd.xlsx
+++ b/artfynd/A 46787-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121432350</v>
+        <v>121432782</v>
       </c>
       <c r="B2" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520544</v>
+        <v>520435</v>
       </c>
       <c r="R2" t="n">
-        <v>6995746</v>
+        <v>6995794</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121432782</v>
+        <v>121432657</v>
       </c>
       <c r="B3" t="n">
-        <v>79685</v>
+        <v>90713</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520435</v>
+        <v>520484</v>
       </c>
       <c r="R3" t="n">
-        <v>6995794</v>
+        <v>6995781</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121432657</v>
+        <v>121432350</v>
       </c>
       <c r="B4" t="n">
-        <v>90710</v>
+        <v>79688</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520484</v>
+        <v>520544</v>
       </c>
       <c r="R4" t="n">
-        <v>6995781</v>
+        <v>6995746</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 46787-2024 artfynd.xlsx
+++ b/artfynd/A 46787-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121432782</v>
+        <v>121432657</v>
       </c>
       <c r="B2" t="n">
-        <v>79688</v>
+        <v>90719</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520435</v>
+        <v>520484</v>
       </c>
       <c r="R2" t="n">
-        <v>6995794</v>
+        <v>6995781</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121432657</v>
+        <v>121432782</v>
       </c>
       <c r="B3" t="n">
-        <v>90713</v>
+        <v>79689</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520484</v>
+        <v>520435</v>
       </c>
       <c r="R3" t="n">
-        <v>6995781</v>
+        <v>6995794</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
         <v>121432350</v>
       </c>
       <c r="B4" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 46787-2024 artfynd.xlsx
+++ b/artfynd/A 46787-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121432657</v>
+        <v>121432782</v>
       </c>
       <c r="B2" t="n">
-        <v>90719</v>
+        <v>79690</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520484</v>
+        <v>520435</v>
       </c>
       <c r="R2" t="n">
-        <v>6995781</v>
+        <v>6995794</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121432782</v>
+        <v>121432350</v>
       </c>
       <c r="B3" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520435</v>
+        <v>520544</v>
       </c>
       <c r="R3" t="n">
-        <v>6995794</v>
+        <v>6995746</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121432350</v>
+        <v>121432657</v>
       </c>
       <c r="B4" t="n">
-        <v>79689</v>
+        <v>90720</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520544</v>
+        <v>520484</v>
       </c>
       <c r="R4" t="n">
-        <v>6995746</v>
+        <v>6995781</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 46787-2024 artfynd.xlsx
+++ b/artfynd/A 46787-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121432782</v>
+        <v>121432350</v>
       </c>
       <c r="B2" t="n">
         <v>79690</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520435</v>
+        <v>520544</v>
       </c>
       <c r="R2" t="n">
-        <v>6995794</v>
+        <v>6995746</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121432350</v>
+        <v>121432782</v>
       </c>
       <c r="B3" t="n">
         <v>79690</v>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520544</v>
+        <v>520435</v>
       </c>
       <c r="R3" t="n">
-        <v>6995746</v>
+        <v>6995794</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 46787-2024 artfynd.xlsx
+++ b/artfynd/A 46787-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121432782</v>
+        <v>121432657</v>
       </c>
       <c r="B3" t="n">
-        <v>79690</v>
+        <v>90720</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520435</v>
+        <v>520484</v>
       </c>
       <c r="R3" t="n">
-        <v>6995794</v>
+        <v>6995781</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121432657</v>
+        <v>121432782</v>
       </c>
       <c r="B4" t="n">
-        <v>90720</v>
+        <v>79690</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520484</v>
+        <v>520435</v>
       </c>
       <c r="R4" t="n">
-        <v>6995781</v>
+        <v>6995794</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 46787-2024 artfynd.xlsx
+++ b/artfynd/A 46787-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121432350</v>
+        <v>121432657</v>
       </c>
       <c r="B2" t="n">
-        <v>79690</v>
+        <v>90720</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520544</v>
+        <v>520484</v>
       </c>
       <c r="R2" t="n">
-        <v>6995746</v>
+        <v>6995781</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121432657</v>
+        <v>121432350</v>
       </c>
       <c r="B3" t="n">
-        <v>90720</v>
+        <v>79690</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520484</v>
+        <v>520544</v>
       </c>
       <c r="R3" t="n">
-        <v>6995781</v>
+        <v>6995746</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 46787-2024 artfynd.xlsx
+++ b/artfynd/A 46787-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121432657</v>
+        <v>121432350</v>
       </c>
       <c r="B2" t="n">
-        <v>90720</v>
+        <v>79697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520484</v>
+        <v>520544</v>
       </c>
       <c r="R2" t="n">
-        <v>6995781</v>
+        <v>6995746</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121432350</v>
+        <v>121432657</v>
       </c>
       <c r="B3" t="n">
-        <v>79690</v>
+        <v>90728</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520544</v>
+        <v>520484</v>
       </c>
       <c r="R3" t="n">
-        <v>6995746</v>
+        <v>6995781</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
         <v>121432782</v>
       </c>
       <c r="B4" t="n">
-        <v>79690</v>
+        <v>79697</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 46787-2024 artfynd.xlsx
+++ b/artfynd/A 46787-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121432782</v>
+        <v>121432350</v>
       </c>
       <c r="B2" t="n">
         <v>79697</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520435</v>
+        <v>520544</v>
       </c>
       <c r="R2" t="n">
-        <v>6995794</v>
+        <v>6995746</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121432350</v>
+        <v>121432657</v>
       </c>
       <c r="B3" t="n">
-        <v>79697</v>
+        <v>90728</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520544</v>
+        <v>520484</v>
       </c>
       <c r="R3" t="n">
-        <v>6995746</v>
+        <v>6995781</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121432657</v>
+        <v>121432782</v>
       </c>
       <c r="B4" t="n">
-        <v>90728</v>
+        <v>79697</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520484</v>
+        <v>520435</v>
       </c>
       <c r="R4" t="n">
-        <v>6995781</v>
+        <v>6995794</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
